--- a/make_test_file/قوالب/قالب - استمارات قبول المعهد اختبار 5 أجزاء.xlsx
+++ b/make_test_file/قوالب/قالب - استمارات قبول المعهد اختبار 5 أجزاء.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alrag\Desktop\جمعية تحفيظ القرآن\scripts\make_test_file\قوالب\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODE\scripts\make_test_file\قوالب\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9A3F25-232B-4DAA-B007-0923795F7478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232246EC-F713-4F51-A3A3-890ECD7BC5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="استمارة القبول" sheetId="1" r:id="rId1"/>
@@ -673,11 +673,42 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -702,37 +733,6 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -950,15 +950,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Y940"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" customWidth="1"/>
-    <col min="3" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="9" width="20.7109375" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="22" width="9.140625" customWidth="1"/>
-    <col min="23" max="25" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.73046875" customWidth="1"/>
+    <col min="3" max="7" width="15.73046875" customWidth="1"/>
+    <col min="8" max="9" width="20.73046875" customWidth="1"/>
+    <col min="10" max="10" width="10.73046875" customWidth="1"/>
+    <col min="11" max="22" width="9.1328125" customWidth="1"/>
+    <col min="23" max="25" width="8.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="18.75" customHeight="1">
@@ -989,17 +989,17 @@
       <c r="Y1" s="2"/>
     </row>
     <row r="2" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="46" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
       <c r="H2" s="3"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -1047,18 +1047,18 @@
       <c r="Y3" s="2"/>
     </row>
     <row r="4" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="17"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="19"/>
       <c r="F4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="17"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="19"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1078,18 +1078,18 @@
       <c r="Y4" s="2"/>
     </row>
     <row r="5" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="17"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="19"/>
       <c r="F5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="31"/>
-      <c r="H5" s="17"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="19"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1109,16 +1109,16 @@
       <c r="Y5" s="2"/>
     </row>
     <row r="6" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="17"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="19"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1165,16 +1165,16 @@
       <c r="Y7" s="2"/>
     </row>
     <row r="8" spans="1:25" ht="19.5" customHeight="1">
-      <c r="A8" s="19"/>
-      <c r="B8" s="34" t="s">
+      <c r="A8" s="36"/>
+      <c r="B8" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="36"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="5"/>
@@ -1193,14 +1193,14 @@
       <c r="X8" s="2"/>
     </row>
     <row r="9" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A9" s="20"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="39"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="29"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="5"/>
@@ -1219,26 +1219,26 @@
       <c r="X9" s="2"/>
     </row>
     <row r="10" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="23" t="s">
+      <c r="A10" s="38"/>
+      <c r="B10" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="40" t="s">
+      <c r="D10" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="42" t="s">
+      <c r="H10" s="32" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="2"/>
@@ -1259,30 +1259,30 @@
       <c r="X10" s="2"/>
     </row>
     <row r="11" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A11" s="22"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="43"/>
+      <c r="A11" s="39"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="33"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="5"/>
-      <c r="L11" s="44" t="s">
+      <c r="L11" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="M11" s="32" t="s">
+      <c r="M11" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="N11" s="32" t="s">
+      <c r="N11" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="O11" s="32" t="s">
+      <c r="O11" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="32" t="s">
+      <c r="P11" s="22" t="s">
         <v>13</v>
       </c>
       <c r="Q11" s="5"/>
@@ -1295,7 +1295,7 @@
       <c r="X11" s="2"/>
     </row>
     <row r="12" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A12" s="22"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="6">
         <v>1</v>
       </c>
@@ -1311,11 +1311,11 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="5"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
@@ -1326,7 +1326,7 @@
       <c r="X12" s="2"/>
     </row>
     <row r="13" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A13" s="22"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="6">
         <v>2</v>
       </c>
@@ -1372,7 +1372,7 @@
       <c r="X13" s="2"/>
     </row>
     <row r="14" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A14" s="22"/>
+      <c r="A14" s="39"/>
       <c r="B14" s="6">
         <v>3</v>
       </c>
@@ -1418,7 +1418,7 @@
       <c r="X14" s="2"/>
     </row>
     <row r="15" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A15" s="22"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="6">
         <v>4</v>
       </c>
@@ -1464,7 +1464,7 @@
       <c r="X15" s="2"/>
     </row>
     <row r="16" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A16" s="22"/>
+      <c r="A16" s="39"/>
       <c r="B16" s="6">
         <v>5</v>
       </c>
@@ -1474,7 +1474,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="9" t="str">
-        <f>IF(AND(COUNT(C16)&gt;0, COUNT(D16)&gt;0, COUNT(E16)&gt;0, COUNT(F16)&gt;0, COUNT(G16)&gt;0), 10 - SUM(#REF!), "")</f>
+        <f>IF(AND(COUNT(C16)&gt;0, COUNT(D16)&gt;0, COUNT(E16)&gt;0, COUNT(F16)&gt;0, COUNT(G16)&gt;0), 10 - SUM(L16:P16), "")</f>
         <v/>
       </c>
       <c r="I16" s="2"/>
@@ -1510,15 +1510,15 @@
       <c r="X16" s="2"/>
     </row>
     <row r="17" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A17" s="22"/>
-      <c r="B17" s="27" t="s">
+      <c r="A17" s="39"/>
+      <c r="B17" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="29"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="46"/>
       <c r="H17" s="12" t="str">
         <f>IF(AND(H12 = "", H13 = "", H14 = "", H15 = "", H16 = ""), "", (SUM(H12:H16) / (COUNT(H12:H16) * 10)) * 100)</f>
         <v/>
@@ -1541,15 +1541,15 @@
       <c r="X17" s="2"/>
     </row>
     <row r="18" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A18" s="20"/>
-      <c r="B18" s="30" t="s">
+      <c r="A18" s="37"/>
+      <c r="B18" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="17"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="19"/>
       <c r="H18" s="9" t="str">
         <f>IF(H17 = "", "", IF(H17 &gt;= 90, "ممتاز", IF(H17 &gt;= 80, "جيدجدا", IF(H17 &gt;= 60, "جيد", "راسب"))))</f>
         <v/>
@@ -1598,16 +1598,16 @@
       <c r="X19" s="2"/>
     </row>
     <row r="20" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="17"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="19"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -1627,16 +1627,16 @@
       <c r="Y20" s="2"/>
     </row>
     <row r="21" spans="1:25" ht="18.75" customHeight="1">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="17"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -26470,11 +26470,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A18"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="O11:O12"/>
     <mergeCell ref="P11:P12"/>
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="B8:H9"/>
@@ -26486,21 +26496,11 @@
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="N11:N12"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A18"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <conditionalFormatting sqref="H17">
     <cfRule type="colorScale" priority="1">
